--- a/EXCEL/Exercise Files/Chapter05/05_06_MultipleCorrelation.xlsx
+++ b/EXCEL/Exercise Files/Chapter05/05_06_MultipleCorrelation.xlsx
@@ -1,24 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Writing\Lynda\Data Analysis Fundamentals October 2018 Refresh\Exercise Files\Chapter05\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\neha work\Data Analytics\EXCEL\Exercise Files\Chapter05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83A6375F-EFEA-44CA-B167-1339D3FC1B3C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{844B6679-4481-4424-A1F1-479819B3B40C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="288" yWindow="324" windowWidth="22752" windowHeight="11916" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -379,9 +388,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:J12"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -395,7 +404,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="18" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -412,7 +421,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
@@ -426,7 +435,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>7</v>
       </c>
@@ -452,7 +461,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>2</v>
       </c>
@@ -468,8 +477,24 @@
       <c r="F6" s="2" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G6">
+        <f>CORREL($A$3:$A$12,A3:A12)</f>
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ref="H6:J6" si="0">CORREL($A$3:$A$12,B3:B12)</f>
+        <v>-7.0616952177650114E-2</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="0"/>
+        <v>0.73719901064788396</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="0"/>
+        <v>0.48503173467607291</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>3</v>
       </c>
@@ -485,8 +510,24 @@
       <c r="F7" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G7">
+        <f>CORREL($B$3:$B$12,A3:A12)</f>
+        <v>-7.0616952177650114E-2</v>
+      </c>
+      <c r="H7">
+        <f t="shared" ref="H7:J7" si="1">CORREL($B$3:$B$12,B3:B12)</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="1"/>
+        <v>-0.39911706248255019</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="1"/>
+        <v>0.20257937544884455</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>5</v>
       </c>
@@ -502,8 +543,24 @@
       <c r="F8" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G8">
+        <f>CORREL($C$3:$C$12,A3:A12)</f>
+        <v>0.73719901064788396</v>
+      </c>
+      <c r="H8">
+        <f t="shared" ref="H8:J8" si="2">CORREL($C$3:$C$12,B3:B12)</f>
+        <v>-0.39911706248255019</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="2"/>
+        <v>-6.5867221172426202E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -519,8 +576,24 @@
       <c r="F9" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G9">
+        <f>CORREL($D$3:$D$12,A3:A12)</f>
+        <v>0.48503173467607291</v>
+      </c>
+      <c r="H9">
+        <f t="shared" ref="H9:J9" si="3">CORREL($D$3:$D$12,B3:B12)</f>
+        <v>0.20257937544884455</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="3"/>
+        <v>-6.5867221172426202E-2</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>1</v>
       </c>
@@ -534,7 +607,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>6</v>
       </c>
@@ -548,7 +621,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>9</v>
       </c>
